--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6847013</v>
+        <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>106244</v>
+        <v>111332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,39 +1228,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220240</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörttjärns gruvhål, Vstm</t>
@@ -1297,17 +1286,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I barrförna under och kring gran.</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,12 +1300,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Granskog, bäck</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1338,16 +1323,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6847013</t>
+          <t>https://artportalen.se/Sighting/136948573</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6847019</v>
+        <v>6847013</v>
       </c>
       <c r="B7" t="n">
-        <v>97983</v>
+        <v>106244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,26 +1340,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1420,6 +1417,11 @@
           <t>2013-07-01</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I barrförna under och kring gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1431,7 +1433,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1448,16 +1450,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6847019</t>
+          <t>https://artportalen.se/Sighting/6847013</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6847022</v>
+        <v>6847019</v>
       </c>
       <c r="B8" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,16 +1467,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1541,7 +1543,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1558,16 +1560,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6847022</t>
+          <t>https://artportalen.se/Sighting/6847019</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131062648</v>
+        <v>6847022</v>
       </c>
       <c r="B9" t="n">
-        <v>57141</v>
+        <v>97986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,53 +1577,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tarmbäcken, Sura sn, Vstm</t>
+          <t>Mörttjärns gruvhål, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557781</v>
+        <v>557633</v>
       </c>
       <c r="R9" t="n">
-        <v>6625339</v>
+        <v>6625480</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1645,27 +1634,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Förmodligen letabde grus</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1676,81 +1650,78 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131062648</t>
+          <t>https://artportalen.se/Sighting/6847022</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99574566</v>
+        <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>58114</v>
+        <v>103930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Usträngsbotarmen, Vstm</t>
+          <t>Mörttjärns gruvhål, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557389</v>
+        <v>557633</v>
       </c>
       <c r="R10" t="n">
-        <v>6624251</v>
+        <v>6625480</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,27 +1745,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Vid holk nr 57</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1803,75 +1759,88 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Granskog, bäck</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Seppo  Leppälampi</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Seppo  Leppälampi, Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99574566</t>
+          <t>https://artportalen.se/Sighting/136948569</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4222602</v>
+        <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>97983</v>
+        <v>93449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tarmbäcken, Sura sn, Vstm</t>
+          <t>Mörttjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557392</v>
+        <v>557874</v>
       </c>
       <c r="R11" t="n">
-        <v>6624094</v>
+        <v>6625580</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1895,12 +1864,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2010-08-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2010-08-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1909,38 +1878,39 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Skogsbäck/dikad, björkskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4222602</t>
+          <t>https://artportalen.se/Sighting/136948585</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394427</v>
+        <v>131062648</v>
       </c>
       <c r="B12" t="n">
-        <v>97231</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,37 +1918,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fanfluksbäcken, Vstm</t>
+          <t>Tarmbäcken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558068</v>
+        <v>557781</v>
       </c>
       <c r="R12" t="n">
-        <v>6624335</v>
+        <v>6625339</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2002,12 +1988,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Förmodligen letabde grus</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2022,31 +2023,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121394427</t>
+          <t>https://artportalen.se/Sighting/131062648</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1444102</v>
+        <v>99574566</v>
       </c>
       <c r="B13" t="n">
-        <v>93215</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,43 +2051,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fanfluksmossarna, Sura sn, Vstm</t>
+          <t>Usträngsbotarmen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557728</v>
+        <v>557389</v>
       </c>
       <c r="R13" t="n">
-        <v>6624740</v>
+        <v>6624251</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2117,12 +2117,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Vid holk nr 57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,36 +2148,35 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal granskog, fuktstråk</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Seppo  Leppälampi</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Seppo  Leppälampi, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1444102</t>
+          <t>https://artportalen.se/Sighting/99574566</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114186087</v>
+        <v>4222602</v>
       </c>
       <c r="B14" t="n">
-        <v>57141</v>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,53 +2184,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fanfluksmossarna, Sura sn, Vstm</t>
+          <t>Tarmbäcken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557966</v>
+        <v>557392</v>
       </c>
       <c r="R14" t="n">
-        <v>6624449</v>
+        <v>6624094</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2240,27 +2238,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2010-08-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Mycket spår på vägen, letat grus på den plogade vägen</t>
+          <t>2010-08-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2271,6 +2254,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Skogsbäck/dikad, björkskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2280,22 +2268,22 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114186087</t>
+          <t>https://artportalen.se/Sighting/4222602</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>82296345</v>
+        <v>121394427</v>
       </c>
       <c r="B15" t="n">
-        <v>57132</v>
+        <v>97231</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,49 +2291,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluksbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557983</v>
+        <v>558068</v>
       </c>
       <c r="R15" t="n">
-        <v>6624408</v>
+        <v>6624335</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2369,27 +2345,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På grusväg</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2404,74 +2365,75 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82296345</t>
+          <t>https://artportalen.se/Sighting/121394427</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131205070</v>
+        <v>1444102</v>
       </c>
       <c r="B16" t="n">
-        <v>57132</v>
+        <v>93215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluksmossarna, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557876</v>
+        <v>557728</v>
       </c>
       <c r="R16" t="n">
-        <v>6624554</v>
+        <v>6624740</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2498,27 +2460,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fina spår i snön</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2529,6 +2476,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal granskog, fuktstråk</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2544,16 +2496,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131205070</t>
+          <t>https://artportalen.se/Sighting/1444102</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130637083</v>
+        <v>114186087</v>
       </c>
       <c r="B17" t="n">
-        <v>57144</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,21 +2513,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2591,23 +2543,23 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fanfluken NV, Ramnäs sn, Vstm</t>
+          <t>Fanfluksmossarna, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557965</v>
+        <v>557966</v>
       </c>
       <c r="R17" t="n">
-        <v>6624427</v>
+        <v>6624449</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2631,22 +2583,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Mycket spår på vägen, letat grus på den plogade vägen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2661,27 +2618,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
+          <t>Sören Larsson, Greta Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130637083</t>
+          <t>https://artportalen.se/Sighting/114186087</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4250025</v>
+        <v>82296345</v>
       </c>
       <c r="B18" t="n">
-        <v>97986</v>
+        <v>57132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,34 +2646,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fanfluksmossarna, Sura sn, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557728</v>
+        <v>557983</v>
       </c>
       <c r="R18" t="n">
-        <v>6624740</v>
+        <v>6624408</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2743,12 +2712,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På grusväg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2759,11 +2743,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal granskog, fuktstråk</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2773,22 +2752,22 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Sören Larsson, Greta Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4250025</t>
+          <t>https://artportalen.se/Sighting/82296345</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5983084</v>
+        <v>131205070</v>
       </c>
       <c r="B19" t="n">
-        <v>99038</v>
+        <v>57132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2796,30 +2775,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223597</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Usträngsbotarmskogen, Sura sn, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557791</v>
+        <v>557876</v>
       </c>
       <c r="R19" t="n">
-        <v>6624400</v>
+        <v>6624554</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2846,12 +2841,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2010-08-05</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2010-08-05</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fina spår i snön</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2862,11 +2872,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Skogskärr med liten bäck igenom</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2882,16 +2887,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5983084</t>
+          <t>https://artportalen.se/Sighting/131205070</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5983085</v>
+        <v>130637083</v>
       </c>
       <c r="B20" t="n">
-        <v>99038</v>
+        <v>57144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2899,33 +2904,53 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223597</v>
+        <v>102613</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Usträngsbotarmskogen, Sura sn, Vstm</t>
+          <t>Fanfluken NV, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557783</v>
+        <v>557965</v>
       </c>
       <c r="R20" t="n">
-        <v>6624418</v>
+        <v>6624427</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2949,12 +2974,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2010-08-05</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2010-08-05</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2965,36 +3000,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Skogskärr med liten bäck igenom</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5983085</t>
+          <t>https://artportalen.se/Sighting/130637083</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5985560</v>
+        <v>4250025</v>
       </c>
       <c r="B21" t="n">
-        <v>99038</v>
+        <v>97986</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3002,19 +3032,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3088,54 +3122,50 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5985560</t>
+          <t>https://artportalen.se/Sighting/4250025</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394457</v>
+        <v>5983084</v>
       </c>
       <c r="B22" t="n">
-        <v>92328</v>
+        <v>99038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040162</v>
+        <v>223597</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Timmerbacksmyren, SV, Vstm</t>
+          <t>Usträngsbotarmskogen, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557929</v>
+        <v>557791</v>
       </c>
       <c r="R22" t="n">
-        <v>6624506</v>
+        <v>6624400</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3159,12 +3189,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2010-08-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2010-08-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,27 +3203,340 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Skogskärr med liten bäck igenom</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5983084</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5983085</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Usträngsbotarmskogen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>557783</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6624418</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2010-08-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2010-08-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Skogskärr med liten bäck igenom</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5983085</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5985560</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fanfluksmossarna, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>557728</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6624740</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2011-08-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2011-08-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gammal granskog, fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5985560</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121394457</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Timmerbacksmyren, SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>557929</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6624506</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Ralf Lundmark</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Ralf Lundmark</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121394457</t>
         </is>
@@ -3222,6 +3565,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103930</v>
+        <v>103936</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103936</v>
+        <v>103938</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103938</v>
+        <v>103939</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103939</v>
+        <v>103945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103945</v>
+        <v>103949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103951</v>
+        <v>103953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103953</v>
+        <v>103966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103966</v>
+        <v>103968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103968</v>
+        <v>103971</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103971</v>
+        <v>103986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103986</v>
+        <v>103987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103987</v>
+        <v>103992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103992</v>
+        <v>103995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>103995</v>
+        <v>104001</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>104001</v>
+        <v>104002</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>104002</v>
+        <v>104014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>104014</v>
+        <v>104015</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>104015</v>
+        <v>104018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>104018</v>
+        <v>104019</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 920-2026 artfynd.xlsx
+++ b/artfynd/S 920-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>136948573</v>
       </c>
       <c r="B6" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>136948569</v>
       </c>
       <c r="B10" t="n">
-        <v>104019</v>
+        <v>104023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>136948585</v>
       </c>
       <c r="B11" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
